--- a/AppLogSolutionLocale/dati/nuovi_codici_consegna.xlsx
+++ b/AppLogSolutionLocale/dati/nuovi_codici_consegna.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolutionLocale\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14B8791-359D-4EDF-9500-3A8F9DFD624A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D545522B-1E28-46F5-B56E-EF76CAC6050E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36060" yWindow="768" windowWidth="16860" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nuovi Codici" sheetId="1" r:id="rId1"/>
@@ -404,20 +404,20 @@
   <dimension ref="A1:N1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">

--- a/AppLogSolutionLocale/dati/nuovi_codici_consegna.xlsx
+++ b/AppLogSolutionLocale/dati/nuovi_codici_consegna.xlsx
@@ -1,85 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolutionLocale\dati\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D545522B-1E28-46F5-B56E-EF76CAC6050E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="36060" yWindow="768" windowWidth="16860" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Nuovi Codici" sheetId="1" r:id="rId1"/>
+    <sheet name="Nuovi Codici" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>Codice Frutta</t>
-  </si>
-  <si>
-    <t>Codice Latte</t>
-  </si>
-  <si>
-    <t>A chi va consegnato</t>
-  </si>
-  <si>
-    <t>Tipologia grado</t>
-  </si>
-  <si>
-    <t>Indirizzo</t>
-  </si>
-  <si>
-    <t>CAP</t>
-  </si>
-  <si>
-    <t>Città</t>
-  </si>
-  <si>
-    <t>Provincia</t>
-  </si>
-  <si>
-    <t>Tipologia consegna</t>
-  </si>
-  <si>
-    <t>Tipologia consegna.1</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Sito web</t>
-  </si>
-  <si>
-    <t>Orario min</t>
-  </si>
-  <si>
-    <t>Orario max</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -98,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -400,68 +408,408 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.109375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Codice Frutta</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Codice Latte</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>A chi va consegnato</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Tipologia grado</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CAP</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Città</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Tipologia consegna</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Tipologia consegna.1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Sito web</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Orario min</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Orario max</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>100345575</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ALMAVITE - ENO CACCIA C.S.S.A. ONLUS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>GRAND CHEF</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>LOCALITA  COLOMBARINO  1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>DESENZANO</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>BS</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>100353794</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GORNI STEFANO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>GRAND CHEF</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>VIA PALMIRO TOGLIATTI 13/A</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SAN GIORGIO BIGARELLO</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>100353958</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VILLA BEVILACQUA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GRAND CHEF</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>VIA ROMA 50</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BEVILACQUA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>VR</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>100354300</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HOTEL LAGO DI GARDA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>GRAND CHEF</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PIAZZA VITTORIO EMANUELE 2</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MALCESINE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>VR</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>100354691</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RISTORANTE - HOTEL BAIA VERDE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GRAND CHEF</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>VIA GARDESANA 142</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MALCESINE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>VR</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>100354885</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RISTORANTE GALATEO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>GRAND CHEF</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>VIA BASSONE 163/A</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VERONA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>VR</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>100355212</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DOME BISTROT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>GRAND CHEF</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>VIA NAZIONALE DEL BRENNERO 21</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SAN PIETRO IN CARIANO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>VR</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/AppLogSolutionLocale/dati/nuovi_codici_consegna.xlsx
+++ b/AppLogSolutionLocale/dati/nuovi_codici_consegna.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolutionLocale\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0533388-C9C5-4F05-AEFA-FBF2034B54D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A4AE50-11D9-4783-8321-BED0A73B14E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30000" yWindow="852" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nuovi Codici" sheetId="1" r:id="rId1"/>

--- a/AppLogSolutionLocale/dati/nuovi_codici_consegna.xlsx
+++ b/AppLogSolutionLocale/dati/nuovi_codici_consegna.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolutionLocale\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A4AE50-11D9-4783-8321-BED0A73B14E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45E9AD8-9295-426A-B809-CCB353B0CB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/AppLogSolutionLocale/dati/nuovi_codici_consegna.xlsx
+++ b/AppLogSolutionLocale/dati/nuovi_codici_consegna.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolutionLocale\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45E9AD8-9295-426A-B809-CCB353B0CB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F011A1-5218-4D48-8B21-70057EFC3642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25944" yWindow="1836" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nuovi Codici" sheetId="1" r:id="rId1"/>

--- a/AppLogSolutionLocale/dati/nuovi_codici_consegna.xlsx
+++ b/AppLogSolutionLocale/dati/nuovi_codici_consegna.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolutionLocale\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F011A1-5218-4D48-8B21-70057EFC3642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DDC3F7-803C-4A3A-9086-F0FCB4F172AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25944" yWindow="1836" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="852" yWindow="1104" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nuovi Codici" sheetId="1" r:id="rId1"/>

--- a/AppLogSolutionLocale/dati/nuovi_codici_consegna.xlsx
+++ b/AppLogSolutionLocale/dati/nuovi_codici_consegna.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\App\AppLogSolutionLocale\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DDC3F7-803C-4A3A-9086-F0FCB4F172AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0978F0D-E902-457B-B208-D195CE4DFC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="852" yWindow="1104" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="456" yWindow="516" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nuovi Codici" sheetId="1" r:id="rId1"/>
